--- a/data/Long-Chinesisch_Lektionen.xlsx
+++ b/data/Long-Chinesisch_Lektionen.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Robert Ruhe\Downloads\flashcards HSK\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D73A499D-A2CA-4FE1-BA64-B2621A6B88D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{522CD95F-8F0A-4D2F-8CA8-D4DC56A33A7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Long - Master" sheetId="1" r:id="rId1"/>
     <sheet name="HSK 1" sheetId="25" r:id="rId2"/>
     <sheet name="HSK 2" sheetId="26" r:id="rId3"/>
-    <sheet name="HSK 3-1" sheetId="27" r:id="rId4"/>
-    <sheet name="HSK 3-2" sheetId="32" r:id="rId5"/>
-    <sheet name="HSK 4-1" sheetId="28" r:id="rId6"/>
+    <sheet name="HSK 3 1" sheetId="27" r:id="rId4"/>
+    <sheet name="HSK 3 2" sheetId="32" r:id="rId5"/>
+    <sheet name="HSK 4 1" sheetId="28" r:id="rId6"/>
     <sheet name="HSK 4-2" sheetId="29" r:id="rId7"/>
     <sheet name="HSK 4-3" sheetId="30" r:id="rId8"/>
     <sheet name="HSK 4-4" sheetId="31" r:id="rId9"/>
@@ -26,27 +26,27 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'HSK 1'!$A$1:$H$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'HSK 2'!$A$1:$H$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'HSK 3-1'!$A$1:$H$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'HSK 3-2'!$A$1:$H$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'HSK 4-1'!$A$1:$H$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'HSK 3 1'!$A$1:$H$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'HSK 3 2'!$A$1:$H$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'HSK 4 1'!$A$1:$H$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'HSK 4-2'!$A$1:$H$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'HSK 4-3'!$A$1:$H$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'HSK 4-4'!$A$1:$H$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Long - Master'!$A$1:$I$899</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'HSK 1'!$A$1:$H$76</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'HSK 2'!$A$1:$H$76</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'HSK 3-1'!$A$1:$H$76</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'HSK 3-2'!$A$1:$H$73</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'HSK 4-1'!$A$1:$H$76</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'HSK 3 1'!$A$1:$H$76</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'HSK 3 2'!$A$1:$H$73</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'HSK 4 1'!$A$1:$H$76</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'HSK 4-2'!$A$1:$H$76</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'HSK 4-3'!$A$1:$H$76</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'HSK 4-4'!$A$1:$H$76</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Long - Master'!$A$1:$H$948</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'HSK 1'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'HSK 2'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'HSK 3-1'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'HSK 3-2'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'HSK 4-1'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'HSK 3 1'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'HSK 3 2'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'HSK 4 1'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'HSK 4-2'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'HSK 4-3'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'HSK 4-4'!$1:$1</definedName>

--- a/data/Long-Chinesisch_Lektionen.xlsx
+++ b/data/Long-Chinesisch_Lektionen.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Robert Ruhe\Downloads\flashcards HSK\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{522CD95F-8F0A-4D2F-8CA8-D4DC56A33A7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7815DB0-63A5-4575-91C3-E5C3719A9FD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Long - Master" sheetId="1" r:id="rId1"/>
     <sheet name="HSK 1" sheetId="25" r:id="rId2"/>
     <sheet name="HSK 2" sheetId="26" r:id="rId3"/>
-    <sheet name="HSK 3 1" sheetId="27" r:id="rId4"/>
+    <sheet name="HSK 3" sheetId="27" r:id="rId4"/>
     <sheet name="HSK 3 2" sheetId="32" r:id="rId5"/>
     <sheet name="HSK 4 1" sheetId="28" r:id="rId6"/>
     <sheet name="HSK 4-2" sheetId="29" r:id="rId7"/>
@@ -26,7 +26,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'HSK 1'!$A$1:$H$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'HSK 2'!$A$1:$H$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'HSK 3 1'!$A$1:$H$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'HSK 3'!$A$1:$H$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'HSK 3 2'!$A$1:$H$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'HSK 4 1'!$A$1:$H$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'HSK 4-2'!$A$1:$H$29</definedName>
@@ -35,7 +35,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Long - Master'!$A$1:$I$899</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'HSK 1'!$A$1:$H$76</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'HSK 2'!$A$1:$H$76</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'HSK 3 1'!$A$1:$H$76</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'HSK 3'!$A$1:$H$76</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'HSK 3 2'!$A$1:$H$73</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'HSK 4 1'!$A$1:$H$76</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'HSK 4-2'!$A$1:$H$76</definedName>
@@ -44,7 +44,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Long - Master'!$A$1:$H$948</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'HSK 1'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'HSK 2'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'HSK 3 1'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'HSK 3'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'HSK 3 2'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'HSK 4 1'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'HSK 4-2'!$1:$1</definedName>

--- a/data/Long-Chinesisch_Lektionen.xlsx
+++ b/data/Long-Chinesisch_Lektionen.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Robert Ruhe\Downloads\flashcards HSK\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7815DB0-63A5-4575-91C3-E5C3719A9FD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF01A760-87E5-4B4F-91C6-279BBCEAC3F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Long - Master" sheetId="1" r:id="rId1"/>
     <sheet name="HSK 1" sheetId="25" r:id="rId2"/>
     <sheet name="HSK 2" sheetId="26" r:id="rId3"/>
-    <sheet name="HSK 3" sheetId="27" r:id="rId4"/>
-    <sheet name="HSK 3 2" sheetId="32" r:id="rId5"/>
-    <sheet name="HSK 4 1" sheetId="28" r:id="rId6"/>
+    <sheet name="HSK 3-1" sheetId="27" r:id="rId4"/>
+    <sheet name="HSK 3-2" sheetId="32" r:id="rId5"/>
+    <sheet name="HSK 4-1" sheetId="28" r:id="rId6"/>
     <sheet name="HSK 4-2" sheetId="29" r:id="rId7"/>
     <sheet name="HSK 4-3" sheetId="30" r:id="rId8"/>
     <sheet name="HSK 4-4" sheetId="31" r:id="rId9"/>
@@ -26,27 +26,27 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'HSK 1'!$A$1:$H$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'HSK 2'!$A$1:$H$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'HSK 3'!$A$1:$H$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'HSK 3 2'!$A$1:$H$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'HSK 4 1'!$A$1:$H$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'HSK 3-1'!$A$1:$H$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'HSK 3-2'!$A$1:$H$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'HSK 4-1'!$A$1:$H$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'HSK 4-2'!$A$1:$H$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'HSK 4-3'!$A$1:$H$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'HSK 4-4'!$A$1:$H$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Long - Master'!$A$1:$I$899</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'HSK 1'!$A$1:$H$76</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'HSK 2'!$A$1:$H$76</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'HSK 3'!$A$1:$H$76</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'HSK 3 2'!$A$1:$H$73</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'HSK 4 1'!$A$1:$H$76</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'HSK 3-1'!$A$1:$H$76</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'HSK 3-2'!$A$1:$H$73</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'HSK 4-1'!$A$1:$H$76</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'HSK 4-2'!$A$1:$H$76</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'HSK 4-3'!$A$1:$H$76</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'HSK 4-4'!$A$1:$H$76</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Long - Master'!$A$1:$H$948</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'HSK 1'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'HSK 2'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'HSK 3'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'HSK 3 2'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'HSK 4 1'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'HSK 3-1'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'HSK 3-2'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'HSK 4-1'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'HSK 4-2'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'HSK 4-3'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'HSK 4-4'!$1:$1</definedName>
